--- a/Result/checksun_type/安全營運與事件回應.xlsx
+++ b/Result/checksun_type/安全營運與事件回應.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>127.6</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>129.12</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>135.04</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>129.12</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>135.04</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>165.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>855.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>855</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1214.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>8039.18</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>8039.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-639.1600325909847</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>165</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>128.1</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>129.35</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>135.2</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>129.35</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>135.2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>1407.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1060.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1060</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1464.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>8176.96</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>8176.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-620.2180918041115</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>1407</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1407.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>128.6</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>129.65</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>135.38</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>129.65</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>135.38</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>642.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1484.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1484.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1478.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>8227.6</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>8227.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-704.0789588298599</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>642</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>642.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>129.2</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>129.98</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>135.57</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>129.98</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>135.57</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>893.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>1384.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>1384.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1717.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>8320.08</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>8320.08</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-716.7702346227197</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>893</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>893.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>129.2</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>130.25</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>135.75</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>130.25</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>135.75</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1168.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1444.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1444</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1970.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>8343.14</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>8343.139999999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-736.1945488045649</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1168</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1168.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>129.3</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>130.52</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>135.92</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>130.52</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>135.92</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>1190.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1573.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>1573.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1946.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>8449.96</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>8449.959999999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-767.1151923213242</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>1190</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>1190.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>129.5</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>130.85</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>136.03</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>130.85</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>136.03</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>3531.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1869.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1869.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>2049.1</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>8530.9</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>8530.9</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-786.2477119052182</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>3531</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>3531.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>129.4</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>131.25</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>136.11</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>131.25</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>136.11</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>140.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1471.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1471.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1931.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>8559.8</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>8559.799999999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-1036.321035885595</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>140</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>129.1</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>131.65</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>136.17</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>131.65</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>136.17</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1191.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>2051.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>2051.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>2334.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>8618.78</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>8618.780000000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-993.2357474330761</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1191</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1191.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>129.2</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>132.1</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>136.29</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>136.29</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1817.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>2496.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>2496.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>2733.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>8676.66</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>8676.66</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-1008.819772949725</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1817</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1817.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>129.3</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>132.57</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>136.36</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>132.57</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>136.36</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>2668.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>2320.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>2320</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>2638.8</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>8756.82</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>8756.82</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-1062.12481751102</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>2668</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>2668.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>140.9</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>129.48</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>134.62</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>129.48</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>134.62</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>110381.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>40908.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>40908.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>28596.6</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>23663.72</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>23663.72</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>8628.693577550468</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>110381</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>110381.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>135.9</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>127.85</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>134.92</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>127.85</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>134.92</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>41976.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>22455.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>22455</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>18894.3</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>26343.44</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>26343.44</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>2316.735465570189</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>41976</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>41976.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>132.3</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>126.78</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>135.19</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>126.78</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>135.19</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>29096.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>16528.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>16528</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>16561.1</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>27936.96</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>27936.96</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>546.0190389708587</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>29096</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>29096.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>130.2</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>125.78</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>135.57</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>125.78</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>135.57</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>7801.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>15630.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>15630.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>16015.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>31569.52</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>31569.52</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-623.0765361342892</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>7801</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>7801.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>130.1</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>125.48</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>135.98</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>125.48</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>135.98</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>15289.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>18199.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>18199</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>16421.2</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>37510.8</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>37510.8</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>10.64680429172768</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>15289</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>15289.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>127.5</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>125.12</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>136.03</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>125.12</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>136.03</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>18113.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>16284.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>16284.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>15818.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>39649.04</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>39649.04</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>113.2999047470475</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>18113</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>18113.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>125.8</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>124.95</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>135.89</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>124.95</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>135.89</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>12341.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>15333.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>15333.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>15416.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>40120.88</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>40120.88</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-46.67066262917797</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>12341</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>12341.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>124.0</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>135.67</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>125</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>135.67</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>24609.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>16594.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>16594.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>17368.1</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>40112.92</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>40112.92</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>344.8953362129723</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>24609</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>24609.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>121.9</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>124.85</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>135.35</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>124.85</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>135.35</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>20643.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>16401.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>16401</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>15738.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>40001.22</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>40001.22</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-422.470927448705</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>20643</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>20643.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>121.9</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>124.98</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>135.01</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>124.98</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>135.01</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>5717.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>14643.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>14643.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>14736.8</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>40019.04</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>40019.04</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-1078.69162812793</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>5717</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>5717.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>123.0</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>125.58</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>135.01</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>125.58</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>135.01</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>13358.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>15351.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>15351.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>15299.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>40571.72</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>40571.72</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-378.4107852365396</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>13358</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>13358.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>43.26000000000001</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>45.32</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>48.57</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>45.32</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>48.57</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>923.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>639.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>639.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>649.6</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>966.14</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>966.14</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-131.9181011073526</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>923</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>923.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>43.41</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>45.57</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>519.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>498.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>498.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>1102.2</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1091.02</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1091.02</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-165.5805573496141</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>519</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>519.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>43.54</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>45.86</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>48.95</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>48.95</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>44.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>645.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>645.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>1107.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1099.2</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1099.2</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-164.4704749332157</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>44</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>44.15</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>46.21</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>49.14</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>49.14</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>957.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>797.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>797</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>1146.9</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1109.02</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1109.02</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-106.1178402336029</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>957</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>957.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>45.15</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>46.53</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>49.32</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>49.32</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>753.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>692.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>692.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>1094.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1124.12</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1124.12</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-116.7884392258132</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>753</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>753.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>45.91</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>46.82</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>49.48</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>49.48</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>221.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>660.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>660</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1132.9</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1171.46</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1171.46</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-106.003993528049</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>221</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>221.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>46.72</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>47.15</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>49.68</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>49.68</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>1253.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>1705.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>1705.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1264.1</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1197.88</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1197.88</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-29.8117856195272</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>1253</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>1253.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>47.47000000000001</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>47.51</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>49.89</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>47.51</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>49.89</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>801.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1569.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1569.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1197.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1178.44</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1178.44</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-30.47249626379858</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>801</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>801.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>47.98999999999999</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>47.7</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>50.03</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>50.03</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>434.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1496.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1496.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1365.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1182.34</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1182.34</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>18.10050625380677</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>434</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>434.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>47.45</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>47.81</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>50.12</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>50.12</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>591.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1496.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1496</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1788.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1213.76</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1213.76</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>126.1654917698927</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>591</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>591.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>47.42</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>47.92</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>50.23</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>50.23</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>5449.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1605.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1605.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1990.9</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1227.62</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1227.62</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>259.2167035153764</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>5449</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>5449.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>118.5</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>123.48</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>129.32</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>123.48</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>129.32</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>6660.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>12370.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>12370.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>11313.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>10664.12</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>10664.12</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>290.3377297371826</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>6660</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>6660.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>118.0</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>124.02</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>129.76</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>124.02</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>129.76</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>29419.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>11922.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>11922.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>11723.9</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>10870.2</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>10870.2</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>944.5084424789566</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>29419</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>29419.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>116.9</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>124.38</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>130.18</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>124.38</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>130.18</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>5943.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>9621.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>9621.200000000001</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>9433.9</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>10840.14</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>10840.14</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-593.1586979784715</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>5943</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>5943.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>117.0</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>124.92</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>130.66</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>124.92</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>130.66</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>10780.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>12262.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>12262.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>10051.1</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>10994.02</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>10994.02</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-253.3560879898541</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>10780</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>10780.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>118.4</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>125.62</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>131.24</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>125.62</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>131.24</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>9050.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>11437.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>11437.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>12216.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>11031.66</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>11031.66</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-277.1253562921902</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>9050</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>9050.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>119.7</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>126.25</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>131.73</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>126.25</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>131.73</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>4419.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>10257.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>10257.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>11815.6</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>11063.98</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>11063.98</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-115.8269768565206</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>4419</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>4419.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>121.4</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>126.92</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>132.23</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>126.92</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>132.23</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>17914.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>11525.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>11525.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>13900.8</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>11172.64</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>11172.64</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>614.9145286535986</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>17914</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>17914.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>123.6</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>127.58</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>132.75</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>127.58</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>132.75</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>19150.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>9246.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>9246.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>13869.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>11003.34</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>11003.34</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>190.9768747875678</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>19150</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>19150.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>125.2</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>128.1</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>133.25</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>133.25</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>6654.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>7839.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>7839.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>13568.0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>10936.96</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>10936.96</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-553.8975191206046</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>6654</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>6654.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>125.4</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>128.48</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>133.68</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>128.48</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>133.68</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>3150.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>12996.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>12996.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>13330.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>11162.8</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>11162.8</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-259.3645990208279</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>3150</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>3150.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>125.8</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>128.78</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>134.13</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>128.78</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>134.13</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>10760.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>13373.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>13373.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>13784.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>11403.4</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>11403.4</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>546.0883082295968</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>10760</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>10760.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>630.2</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>694.75</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>770.74</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>694.75</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>770.74</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>95711.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>184090.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>184090</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>238520.8</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>625496.02</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>625496.02</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-59407.18447863078</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>95711</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>95711.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>630.2</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>701.25</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>771.56</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>701.25</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>771.5599999999999</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>181105.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>213249.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>213249.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>261286.0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>631907.8</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>631907.8</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-54134.00295314955</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>181105</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>181105.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>631.4</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>706.0</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>772.34</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>706</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>772.34</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>135802.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>252624.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>252624</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>286992.7</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>639483.2</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>639483.2</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-53816.8863827067</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>135802</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>135802.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>641.0</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>712.35</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>773.42</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>712.35</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>773.42</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>262274.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>287562.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>287562.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>323456.1</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>664782.5</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>664782.5</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-46587.93819697743</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>262274</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>262274.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>657.8</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>718.95</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>774.36</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>718.95</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>774.36</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>245558.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>296429.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>296429.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>325427.2</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>674644.66</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>674644.66</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-48147.58585318638</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>245558</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>245558.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>671.6</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>725.65</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>773.56</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>725.65</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>773.5599999999999</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>241508.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>292951.6</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>292951.6</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>382000.7</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>675976.12</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>675976.12</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-46865.09729587106</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>241508</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>241508.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>686.2</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>733.3</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>772.84</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>733.3</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>772.84</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>377978.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>309322.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>309322.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>400021.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>677723.46</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>677723.46</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-42925.28873913951</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>377978</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>377978.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>702.8</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>740.6</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>771.72</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>740.6</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>771.72</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>310495.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>321361.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>321361.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>392151.7</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>673300.18</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>673300.1800000001</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-50385.73048883944</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>310495</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>310495.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>711.8</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>747.5</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>770.14</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>747.5</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>770.14</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>306608.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>359349.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>359349.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>389319.8</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>672018.02</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>672018.02</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-52013.69261380937</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>306608</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>306608.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>722.4</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>754.55</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>768.06</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>754.55</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>768.0599999999999</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>228169.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>354425.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>354425</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>390521.3</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>675976.46</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>675976.46</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-52065.25662755885</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>228169</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>228169.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>735.0</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>760.7</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>766.1</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>760.7</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>766.1</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>323363.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>471049.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>471049.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>445989.1</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>679269.88</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>679269.88</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-41875.26748193102</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>323363</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>323363.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>163.7</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>169.42</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>173.45</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>169.42</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>173.45</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>2205.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>4928.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>4928.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>8212.4</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>9228.52</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>9228.52</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-949.8432312904224</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>2205</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>2205.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>162.7</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>169.8</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>173.78</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>169.8</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>173.78</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>1806.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>5230.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>5230</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>8328.4</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>9360.42</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>9360.42</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-674.4217845078238</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>1806</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>1806.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>162.0</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>170.22</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>174.17</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>170.22</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>174.17</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>2091.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>7426.8</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>7426.8</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>9078.1</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>9486.16</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>9486.16</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-214.1260825145455</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>2091</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>2091.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>162.4</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>170.8</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>174.55</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>170.8</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>174.55</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>13333.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>13295.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>13295</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>9171.4</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>9705.98</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>9705.98</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>420.5508518513707</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>13333</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>13333.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>164.3</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>171.45</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>175.06</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>171.45</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>175.06</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>5209.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>11773.6</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>11773.6</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>8913.7</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>9626.86</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>9626.860000000001</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>107.7125133794161</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>5209</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>5209.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>166.0</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>172.0</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>175.52</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>172</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>175.52</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>3711.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>11496.0</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>11496</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>8727.5</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>9667.6</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>9667.6</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>527.382297227361</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>3711</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>3711.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>168.3</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>172.65</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>175.97</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>172.65</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>175.97</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>12790.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>11426.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>11426.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>9365.7</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>10001.58</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>10001.58</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>1268.575477823444</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>12790</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>12790.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>170.1</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>173.22</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>176.38</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>173.22</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>176.38</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>31432.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>10729.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>10729.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>8877.0</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>9769.86</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>9769.860000000001</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>1309.366611609872</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>31432</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>31432.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>171.5</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>173.68</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>176.68</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>173.68</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>176.68</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>5726.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>5047.8</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>5047.8</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>6725.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>9301.64</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>9301.639999999999</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-676.4805762527285</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>5726</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>5726.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>171.9</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>173.95</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>176.93</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>173.95</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>176.93</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>3821.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>6053.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>6053.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>7435.1</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>9730.8</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>9730.799999999999</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-735.0308240474169</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>3821</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>3821.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>172.4</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>174.12</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>177.18</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>174.12</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>177.18</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>3365.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>5959.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>5959</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>7590.7</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>9802.16</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>9802.16</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-588.3157914667072</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>3365</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>3365.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>18.01</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>18.55</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>19.23</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>19.23</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>1267.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>929.4</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>929.4</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>1477.7</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>1615.24</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>1615.24</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-113.9833348936809</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>1267</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>1267.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>18.03</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>19.27</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>938.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>1032.8</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>1032.8</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>1454.5</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>1633.92</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>1633.92</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-129.3213470370649</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>938</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>938.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>18.06</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>18.67</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>19.31</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>19.31</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>456.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>1421.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>1421.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>1522.3</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>1648.04</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>1648.04</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-111.3641734191469</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>456</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>456.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>18.11</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>19.36</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>19.36</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>1015.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>1799.6</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>1799.6</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>1812.4</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>1720.44</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>1720.44</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-30.09091920000878</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>1015</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>1015.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>18.25</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>18.84</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>19.42</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>19.42</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>971.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>1795.8</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>1795.8</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>1873.7</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>1786.08</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>1786.08</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>27.19554822733176</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>971</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>971.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>18.31</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>19.47</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>1784.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>2026.0</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>2026</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>1876.4</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>1842.62</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>1842.62</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>112.7763749725561</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>1784</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>1784.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>18.43</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>18.97</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>19.52</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>19.52</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>2880.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>1876.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>1876.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>1779.1</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>1829.1</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>1829.1</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>143.8998283595713</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>2880</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>2880.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>18.54</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>19.56</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>2348.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>1623.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>1623.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>1839.5</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>1781.6</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>1781.6</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>65.79405361389377</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>2348</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>2348.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>18.67</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>19.6</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>996.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>1825.2</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>1825.2</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>1668.7</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>1769.68</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>1769.68</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>8.86458777671578</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>996</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>996.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>18.77</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>19.15</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>19.63</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>19.63</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>2122.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>1951.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>1951.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>1698.3</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>1778.96</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>1778.96</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>72.07732987443546</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>2122</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>2122.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>18.86</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>19.67</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>19.67</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>1035.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>1726.8</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>1726.8</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>1601.0</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>1803.6</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>1803.6</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>39.16419966137687</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>1035</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>1035.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>96.04</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>95.58</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>97.19</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>95.58</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>97.19</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>810653.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>785203.4</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>785203.4</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>1528366.9</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>2315754.58</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>2315754.58</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-430919.5205664954</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>810653</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>810653.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>95.74000000000001</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>95.58</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>97.22</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>95.58</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>97.22</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>105063.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>654967.8</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>654967.8</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>1510205.6</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>2358195.7</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>2358195.7</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-442617.8445507861</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>105063</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>105063.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>95.62</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>95.64</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>97.28</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>95.64</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>97.28</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>1085702.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>1012522.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>1012522</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>1796122.0</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>2439791.64</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>2439791.64</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-367923.0272229589</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>1085702</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>1085702.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>95.42</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>95.72</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>97.34</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>95.72</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>97.34</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>1009307.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>1783681.8</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>1783681.8</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>2189880.8</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>2464144.06</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>2464144.06</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-353144.5014966712</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>1009307</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>1009307.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>95.4</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>95.82</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>97.41</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>97.41</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>915292.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>1976536.2</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>1976536.2</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>2445139.9</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>2486742.7</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>2486742.7</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-311234.8396913796</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>915292</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>915292.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>95.5</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>95.94</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>97.45</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>95.94</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>97.45</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>159475.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>2271530.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>2271530.4</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>2735937.8</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>2495554.74</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>2495554.74</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-230175.3285519849</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>159475</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>159475.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>95.64000000000001</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>96.08</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>97.48</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>96.08</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>97.48</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>1892834.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>2365443.4</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>2365443.4</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>3345620.9</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>2512335.08</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>2512335.08</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-25175.08661885001</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>1892834</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>1892834.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>95.78</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>96.22</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>97.51</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>96.22</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>97.51000000000001</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>4941501.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>2579722.0</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>2579722</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>3407520.6</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>2488794.78</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>2488794.78</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>82864.47637915798</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>4941501</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>4941501.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>95.84</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>96.36</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>97.54</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>96.36</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>97.54000000000001</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>1973579.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>2596079.8</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>2596079.8</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>3518706.0</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>2408925.82</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>2408925.82</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-92395.62920865696</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>1973579</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>1973579.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>95.76</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>96.48</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>97.56</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>97.56</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>2390263.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>2913743.6</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>2913743.6</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>3583035.2</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>2404449.18</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>2404449.18</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-21475.72186236875</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>2390263</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>2390263.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>95.4</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>96.58</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>97.58</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>96.58</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>97.58</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>629040.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>3200345.2</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>3200345.2</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>3600465.0</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>2404783.52</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>2404783.52</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>35960.70727027021</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>629040</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>629040.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>47.48999999999999</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>50.59</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>50.59</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>23112800.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>21177545.2</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>21177545.2</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>30699388.3</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>61192009.02</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>61192009.02</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-10203788.78446277</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>23112800</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>23112800.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>47.3</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>49.98</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>50.71</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>50.71</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>20270532.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>21528086.8</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>21528086.8</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>31449102.5</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>84167565.12</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>84167565.12</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-10945843.09974174</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>20270532</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>20270532.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>47.31</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>50.16</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>50.9</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>50.9</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>12542363.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>24969506.0</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>24969506</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>31529300.9</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>88371918.18</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>88371918.18000001</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-11310469.01086379</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>12542363</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>12542363.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>47.52</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>50.27</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>50.98</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>50.98</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>23192947.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>32147610.0</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>32147610</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>33419426.5</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>88949945.82</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>88949945.81999999</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-10599399.74065014</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>23192947</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>23192947.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>47.91</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>50.37</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>51.08</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>51.08</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>26769084.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>38898515.4</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>38898515.4</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>37695465.3</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>89246818.86</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>89246818.86</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-10346170.50675027</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>26769084</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>26769084.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>48.31</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>50.47</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>51.15</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>50.47</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>51.15</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>24865508.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>40221231.4</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>40221231.4</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>43748399.2</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>89427812.42</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>89427812.42</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-9998065.904509388</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>24865508</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>24865508.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>49.13</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>50.62</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>51.24</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>51.24</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>37477628.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>41370118.2</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>41370118.2</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>51160034.6</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>89815049.22</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>89815049.22</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-8939745.261861369</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>37477628</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>37477628.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>49.72000000000001</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>50.75</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>51.32</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>51.32</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>48432883.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>38089095.8</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>38089095.8</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>66570876.6</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>90678399.72</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>90678399.72</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-8459880.584440574</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>48432883</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>48432883.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>50.04</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>50.82</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>51.4</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>56947474.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>34691243.0</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>34691243</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>90486295.0</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>91329430.24</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>91329430.23999999</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-8645998.345823705</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>56947474</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>56947474.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>50.2</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>50.91</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>51.48</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>50.91</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>51.48</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>33382664.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>36492415.2</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>36492415.2</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>89804242.4</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>91988592.18</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>91988592.18000001</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-9515372.814020172</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>33382664</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>33382664.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>50.4</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>50.89</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>51.56</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>51.56</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>30609942.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>47275567.0</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>47275567</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>94688158.0</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>93471434.86</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>93471434.86</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-7892700.525228694</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>30609942</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>30609942.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>113.5</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>113.5</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>116.73</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>116.73</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>112340543.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>83884957.4</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>83884957.40000001</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>92567015.4</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>128962851.72</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>128962851.72</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-6628404.990212098</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>112340543</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>112340543.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>111.9</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>113.35</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>116.89</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>116.89</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>58974098.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>70302719.4</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>70302719.40000001</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>91723931.4</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>131489921.5</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>131489921.5</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-10060661.02958468</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>58974098</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>58974098.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>110.6</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>113.22</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>117.14</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>113.22</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>117.14</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>34730094.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>79011670.2</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>79011670.2</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>97832165.5</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>140255988.42</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>140255988.42</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-8886741.227631778</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>34730094</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>34730094.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>110.3</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>113.35</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>117.45</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>117.45</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>91063758.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>109424681.4</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>109424681.4</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>106790826.3</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>147476441.26</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>147476441.26</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-4294757.466712207</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>91063758</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>91063758.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>110.9</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>113.42</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>117.7</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>113.42</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>117.7</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>122316294.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>110930689.2</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>110930689.2</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>110987090.5</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>153296136.82</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>153296136.82</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-3617146.184444517</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>122316294</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>122316294.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>111.4</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>113.4</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>117.89</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>117.89</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>44429353.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>101249073.4</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>101249073.4</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>104384407.6</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>153206478.06</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>153206478.06</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-5868432.274617672</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>44429353</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>44429353.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>113.1</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>113.68</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>118.17</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>113.68</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>118.17</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>102518852.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>113145143.4</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>113145143.4</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>105840526.6</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>154872547.14</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>154872547.14</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>-529939.0007715523</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>102518852</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>102518852.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>114.6</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>113.88</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>118.4</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>113.88</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>118.4</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>186795150.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>116652660.8</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>116652660.8</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>105637562.5</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>154275102.38</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>154275102.38</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>891531.4618933052</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>186795150</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>186795150.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>115.4</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>113.92</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>118.57</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>113.92</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>118.57</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>98593797.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>104156971.2</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>104156971.2</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>106311106.7</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>154409336.0</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>154409336</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>-6139240.215081647</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>98593797</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>98593797.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>115.5</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>113.8</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>118.7</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>118.7</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>73908215.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>111043491.8</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>111043491.8</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>117037307.6</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>156130606.16</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>156130606.16</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>-6513796.210221544</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>73908215</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>73908215.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>115.1</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>113.68</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>118.85</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>113.68</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>118.85</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>103909703.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>107519741.8</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>107519741.8</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>120255891.6</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>159731148.5</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>159731148.5</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-4171356.838627756</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>103909703</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>103909703.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>147.4</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>152.38</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>162.89</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>152.38</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>162.89</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>24025977.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>22069443.8</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>22069443.8</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>38876521.7</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>48446079.94</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>48446079.94</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-3611021.530052178</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>24025977</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>24025977.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>146.4</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>153.18</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>163.27</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>153.18</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>163.27</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>17661917.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>26724891.6</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>26724891.6</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>39351781.0</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>49034184.34</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>49034184.34</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-3352383.651453033</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>17661917</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>17661917.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>145.8</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>163.71</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>154</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>163.71</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>20757282.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>37721431.2</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>37721431.2</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>42011119.6</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>49452058.04</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>49452058.04</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>-2181309.408759505</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>20757282</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>20757282.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>145.7</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>154.85</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>164.12</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>154.85</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>164.12</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>22500479.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>45867104.6</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>45867104.6</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>47656458.6</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>49685855.8</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>49685855.8</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>-762088.5474559143</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>22500479</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>22500479.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>146.7</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>155.8</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>164.59</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>155.8</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>164.59</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>25401564.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>52979779.0</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>52979779</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>47185132.3</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>49884575.96</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>49884575.96</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>1105816.166815504</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>25401564</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>25401564.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>147.6</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>156.57</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>165.04</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>156.57</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>165.04</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>47303216.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>55683599.6</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>55683599.6</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>48088004.5</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>49740798.42</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>49740798.42</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>3423927.502674118</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>47303216</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>47303216.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>149.5</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>157.6</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>165.54</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>157.6</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>165.54</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>72644615.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>51978670.4</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>51978670.4</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>45211777.8</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>49699632.24</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>49699632.24</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>4266626.428805202</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>72644615</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>72644615.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>150.9</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>158.6</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>166.02</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>158.6</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>166.02</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>61485649.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>46300808.0</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>46300808</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>42600143.9</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>48671879.8</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>48671879.8</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>2602952.629392281</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>61485649</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>61485649.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>152.1</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>159.52</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>166.41</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>159.52</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>166.41</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>58063851.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>49445812.6</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>49445812.6</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>38730712.9</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>48573325.1</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>48573325.1</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>1328916.679181233</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>58063851</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>58063851.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>153.4</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>160.38</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>166.8</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>160.38</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>166.8</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>38920667.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>41390485.6</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>41390485.6</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>35887625.4</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>48642894.44</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>48642894.44</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>-171974.7739481628</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>38920667</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>38920667.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>154.5</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>161.35</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>167.23</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>161.35</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>167.23</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>28778570.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>40492409.4</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>40492409.4</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>38147945.0</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>49369892.62</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>49369892.62</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>-258908.0364919975</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>28778570</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>28778570.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
